--- a/GameConfig/Datas/运营/服务器配置表.xlsx
+++ b/GameConfig/Datas/运营/服务器配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\运营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B91FCA6-89A3-4F1F-BD28-1BC198023405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAC026A-6E83-4A52-B9A8-1F43F29CD912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60105" yWindow="5265" windowWidth="33795" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="服务器配置表" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -187,6 +187,14 @@
   </si>
   <si>
     <t>黑钟馗4服</t>
+  </si>
+  <si>
+    <t>WorldID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -671,20 +679,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B201DAAC-0F3C-4119-A351-123C8C9F580F}">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="9"/>
-    <col min="2" max="2" width="21.5" style="9" customWidth="1"/>
-    <col min="3" max="3" width="42.25" style="9" customWidth="1"/>
-    <col min="4" max="4" width="40.9140625" style="9" customWidth="1"/>
-    <col min="5" max="6" width="23.4140625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="16.9140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="17.58203125" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="9"/>
+    <col min="2" max="3" width="21.5" style="9" customWidth="1"/>
+    <col min="4" max="4" width="42.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="40.9140625" style="9" customWidth="1"/>
+    <col min="6" max="7" width="23.4140625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="16.9140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="17.58203125" style="9" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -692,31 +700,33 @@
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="9"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="14"/>
       <c r="Q1" s="9"/>
       <c r="R1" s="9"/>
       <c r="S1" s="9"/>
@@ -737,16 +747,17 @@
       <c r="AH1" s="9"/>
       <c r="AI1" s="9"/>
       <c r="AJ1" s="9"/>
-    </row>
-    <row r="2" spans="1:36" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AK1" s="9"/>
+    </row>
+    <row r="2" spans="1:37" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>7</v>
+      <c r="C2" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>7</v>
@@ -754,23 +765,25 @@
       <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="I2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="9"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="14"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
       <c r="S2" s="9"/>
@@ -791,8 +804,9 @@
       <c r="AH2" s="9"/>
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
-    </row>
-    <row r="3" spans="1:36" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AK2" s="9"/>
+    </row>
+    <row r="3" spans="1:37" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
@@ -807,10 +821,10 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="9"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="14"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
@@ -831,8 +845,9 @@
       <c r="AH3" s="9"/>
       <c r="AI3" s="9"/>
       <c r="AJ3" s="9"/>
-    </row>
-    <row r="4" spans="1:36" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AK3" s="9"/>
+    </row>
+    <row r="4" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -840,31 +855,33 @@
         <v>19</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="9"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="14"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
@@ -885,195 +902,220 @@
       <c r="AH4" s="9"/>
       <c r="AI4" s="9"/>
       <c r="AJ4" s="9"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK4" s="9"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B5" s="9">
         <v>1051</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="9">
+        <v>1</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="9">
+      <c r="F5" s="9">
         <v>20051</v>
       </c>
-      <c r="F5" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="G5" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B6" s="9">
         <v>1052</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="9">
+        <v>2</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="9">
+      <c r="F6" s="9">
         <v>20052</v>
       </c>
-      <c r="F6" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="9">
+      <c r="G6" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B7" s="9">
         <v>1053</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="9">
+        <v>3</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="9">
+      <c r="F7" s="9">
         <v>20053</v>
       </c>
-      <c r="F7" s="9" t="b">
+      <c r="G7" s="9" t="b">
         <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>2</v>
       </c>
       <c r="H7" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I7" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B8" s="9">
         <v>1054</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="9">
+        <v>4</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="E8" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="9">
+      <c r="F8" s="9">
         <v>20054</v>
       </c>
-      <c r="F8" s="9" t="b">
+      <c r="G8" s="9" t="b">
         <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>2</v>
       </c>
       <c r="H8" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I8" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B9" s="9">
         <v>1055</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="9">
+        <v>5</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="9">
+      <c r="F9" s="9">
         <v>20055</v>
       </c>
-      <c r="F9" s="9" t="b">
+      <c r="G9" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="H9" s="9">
         <v>3</v>
       </c>
-      <c r="H9" s="9">
+      <c r="I9" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B10" s="9">
         <v>1056</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="9">
+        <v>6</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="E10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="9">
+      <c r="F10" s="9">
         <v>20056</v>
       </c>
-      <c r="F10" s="9" t="b">
+      <c r="G10" s="9" t="b">
         <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>3</v>
       </c>
       <c r="H10" s="9">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I10" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
         <v>1057</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="9">
+        <v>7</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="E11" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="9">
+      <c r="F11" s="9">
         <v>20057</v>
       </c>
-      <c r="F11" s="9" t="b">
+      <c r="G11" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="H11" s="9">
         <v>4</v>
       </c>
-      <c r="H11" s="9">
+      <c r="I11" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B12" s="9">
         <v>1058</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="9">
+        <v>8</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="E12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="9">
+      <c r="F12" s="9">
         <v>20058</v>
       </c>
-      <c r="F12" s="9" t="b">
+      <c r="G12" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="G12" s="9">
+      <c r="H12" s="9">
         <v>4</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameConfig/Datas/运营/服务器配置表.xlsx
+++ b/GameConfig/Datas/运营/服务器配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\运营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAC026A-6E83-4A52-B9A8-1F43F29CD912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38BFAED-3D69-48AF-AD7E-C49F50D69DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="服务器配置表" sheetId="2" r:id="rId1"/>
@@ -213,6 +213,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -220,6 +221,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -766,7 +768,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>36</v>
